--- a/Magestorm2/Server/bit_arithmetic.xlsx
+++ b/Magestorm2/Server/bit_arithmetic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repo\Magestorm2\Magestorm2\Server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B39BD8A-6D64-4461-8DE5-DAC96B20D3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881D6194-B8FC-43F5-9460-D6A6621E7EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30780" yWindow="2025" windowWidth="21600" windowHeight="11295" xr2:uid="{0D90CC46-8ADB-4306-8865-1492617AE930}"/>
+    <workbookView xWindow="-14850" yWindow="1710" windowWidth="13920" windowHeight="11295" xr2:uid="{0D90CC46-8ADB-4306-8865-1492617AE930}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Include</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66,8 +83,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,290 +420,238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCB5BDDE-DA84-4887-9E4C-10CB4A14A17F}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <f>2^A1</f>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D1">
-        <v>0</v>
-      </c>
-      <c r="E1">
-        <f>IF(D1=0,0,B1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f t="shared" ref="B2:B17" si="0">2^A2</f>
         <v>1</v>
       </c>
-      <c r="B2">
-        <f>2^A2</f>
+      <c r="D2">
+        <f>IF(C2=1,2^A2,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D2">
+      <c r="D3">
+        <f t="shared" ref="D3:D17" si="1">IF(C3=1,2^A3,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="E2">
-        <f>IF(D2=0,0,B2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <f>2^A3</f>
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <f>IF(D3=0,0,B3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <f>2^A4</f>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <f>IF(D4=0,0,B4)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <f>2^A5</f>
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <f>IF(D5=0,0,B5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <f>2^A6</f>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>256</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>512</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>2048</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>4096</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>8192</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>16384</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>32768</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <f>SUM(D2:D17)</f>
         <v>32</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <f>IF(D6=0,0,B6)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <f>2^A7</f>
-        <v>64</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <f>IF(D7=0,0,B7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <f>2^A8</f>
-        <v>128</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <f>IF(D8=0,0,B8)</f>
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E9">
-        <f>SUM(E1:E8)</f>
-        <v>170</v>
-      </c>
-      <c r="F9">
-        <f>E9-E19</f>
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>0</v>
-      </c>
-      <c r="B11">
-        <v>-128</v>
-      </c>
-      <c r="D11">
-        <f>D8</f>
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <f>IF(D11=0,0,B11)</f>
-        <v>-128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <f>2^(7-A12)</f>
-        <v>64</v>
-      </c>
-      <c r="D12">
-        <f>D7</f>
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f>IF(D12=0,0,B12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <f>2^(7-A13)</f>
-        <v>32</v>
-      </c>
-      <c r="D13">
-        <f>D6</f>
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <f>IF(D13=0,0,B13)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <f>2^(7-A14)</f>
-        <v>16</v>
-      </c>
-      <c r="D14">
-        <f>D5</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f>IF(D14=0,0,B14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <f>2^(7-A15)</f>
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <f>D4</f>
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <f>IF(D15=0,0,B15)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <f>2^(7-A16)</f>
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <f>D3</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f>IF(D16=0,0,B16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <f>2^(7-A17)</f>
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <f>D2</f>
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <f>IF(D17=0,0,B17)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>7</v>
-      </c>
-      <c r="B18">
-        <f>2^(7-A18)</f>
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <f>D1</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <f>IF(D18=0,0,B18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19">
-        <f>-SUM(B12:B18)</f>
-        <v>-127</v>
-      </c>
-      <c r="E19">
-        <f>SUM(E11:E18)</f>
-        <v>-86</v>
       </c>
     </row>
   </sheetData>

--- a/Magestorm2/Server/bit_arithmetic.xlsx
+++ b/Magestorm2/Server/bit_arithmetic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repo\Magestorm2\Magestorm2\Server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881D6194-B8FC-43F5-9460-D6A6621E7EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C96C51-F091-4F35-A273-FE930D7B5594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14850" yWindow="1710" windowWidth="13920" windowHeight="11295" xr2:uid="{0D90CC46-8ADB-4306-8865-1492617AE930}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0D90CC46-8ADB-4306-8865-1492617AE930}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Index</t>
   </si>
@@ -49,18 +49,295 @@
   <si>
     <t>Include</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">public static final byte </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Statistic_Strength </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2AACB8"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">public static final byte </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Statistic_Dexterity  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2AACB8"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">public static final byte </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Statistic_Constitution  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2AACB8"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">public static final byte </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Statistic_Intellect  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2AACB8"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">public static final byte </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Statistic_Charisma  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2AACB8"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">public static final byte </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FFC77DBB"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Statistic_Wisdom  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2AACB8"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFBCBEC4"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCF8E6D"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.5"/>
+      <color rgb="FFC77DBB"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF2AACB8"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -83,9 +360,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,10 +700,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCB5BDDE-DA84-4887-9E4C-10CB4A14A17F}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -449,8 +729,11 @@
         <f>IF(C2=1,2^A2,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -459,11 +742,14 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D17" si="1">IF(C3=1,2^A3,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D3:D28" si="1">IF(C3=1,2^A3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -475,8 +761,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -488,8 +777,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -501,8 +793,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -510,15 +805,15 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
       <c r="D7">
         <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -531,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -544,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -557,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -570,7 +865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -583,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -596,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -604,12 +899,15 @@
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -622,7 +920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
@@ -635,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -648,10 +946,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <f t="shared" ref="B18:B28" si="2">2^A18</f>
+        <v>65536</v>
+      </c>
       <c r="D18">
-        <f>SUM(D2:D17)</f>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="2"/>
+        <v>131072</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="2"/>
+        <v>262144</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="2"/>
+        <v>524288</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="2"/>
+        <v>1048576</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="2"/>
+        <v>2097152</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="2"/>
+        <v>4194304</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="2"/>
+        <v>8388608</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="2"/>
+        <v>16777216</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="2"/>
+        <v>33554432</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="2"/>
+        <v>67108864</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="D29">
+        <f>SUM(D2:D28)</f>
+        <v>4096</v>
       </c>
     </row>
   </sheetData>

--- a/Magestorm2/Server/bit_arithmetic.xlsx
+++ b/Magestorm2/Server/bit_arithmetic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repo\Magestorm2\Magestorm2\Server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C96C51-F091-4F35-A273-FE930D7B5594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4339923-C1A9-4E7F-BADE-DF3D8CD62148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0D90CC46-8ADB-4306-8865-1492617AE930}"/>
+    <workbookView xWindow="-28905" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{0D90CC46-8ADB-4306-8865-1492617AE930}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -899,12 +899,9 @@
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
       <c r="D14">
         <f t="shared" si="1"/>
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -915,9 +912,12 @@
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1092,7 +1092,7 @@
     <row r="29" spans="1:4">
       <c r="D29">
         <f>SUM(D2:D28)</f>
-        <v>4096</v>
+        <v>8192</v>
       </c>
     </row>
   </sheetData>
